--- a/assets/constructions/examples/ctd_tsmb_face_groove.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_face_groove.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,11 +629,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R610M2008-20/AL41F</t>
+          <t>L010.1508-20/AL41F</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -653,13 +678,13 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
@@ -672,7 +697,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>DUEM_DCON:6</t>
+          <t>DUEM_DCON:7</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -688,7 +713,7 @@
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="R2" t="n">
         <v>20</v>
@@ -697,17 +722,15 @@
         <v>35</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.1</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -717,7 +740,7 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>DUEM_DCON:6</t>
+          <t>DUEM_DCON:7</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -755,13 +778,32 @@
       <c r="AN2" t="inlineStr">
         <is>
           <t>Ultramini.pdf</t>
+        </is>
+      </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>70.04000000000001</v>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AR2" t="n">
+        <v>6439.04</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BTFPW10.066215.RETC</t>
+          <t>BTFPW20.066215.REA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -815,10 +857,10 @@
         <v>42</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
         <v>0.1</v>
@@ -847,12 +889,12 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>VBX</t>
+          <t>VTX</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -875,36 +917,55 @@
       <c r="AN3" t="inlineStr">
         <is>
           <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5245.35</v>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="AR3" t="n">
+        <v>5245.35</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BTFGW30.068015.RKA</t>
+          <t>R010.3008-10/CN45F</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BRICE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>DUEMMEL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ULTRAMINI</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PMKNS</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
+          <t>PMKS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
@@ -918,48 +979,52 @@
       <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>DUEM_DCON:7</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>DUEMMEL</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>4.9</v>
+      </c>
       <c r="O4" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.8</v>
-      </c>
+        <v>4.9</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="R4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="S4" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="T4" t="n">
         <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>6</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.1</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="n">
-        <v>18.3</v>
-      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>VARGUS_D:6</t>
+          <t>DUEM_DCON:7</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -969,12 +1034,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>CN45F</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>AlTiN</t>
+          <t>TIN</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -985,10 +1050,10 @@
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
@@ -996,14 +1061,33 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2021/Groovex VARGUS</t>
+          <t>Ultramini.pdf</t>
+        </is>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>63.68</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AR4" t="n">
+        <v>5854.34</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>PMKS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L010.1008-10/CN45F</t>
+          <t>R610.2008-10/CN45F</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1023,13 +1107,13 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
@@ -1042,7 +1126,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>DUEM_DCON:7</t>
+          <t>DUEM_DCON:6</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1058,7 +1142,7 @@
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="R5" t="n">
         <v>11</v>
@@ -1067,15 +1151,15 @@
         <v>26</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -1085,7 +1169,7 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>DUEM_DCON:7</t>
+          <t>DUEM_DCON:6</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1123,36 +1207,55 @@
       <c r="AN5" t="inlineStr">
         <is>
           <t>Ultramini.pdf</t>
+        </is>
+      </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>60.47</v>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AR5" t="n">
+        <v>5559.23</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>PMKS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BTFGW20.068015.RKA</t>
+          <t>L010M1008-10/AL41F</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BRICE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>DUEMMEL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ULTRAMINI</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>PMKNS</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -1166,48 +1269,54 @@
       <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DUEM_DCON:7</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>DUEMMEL</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>5.6</v>
+      </c>
       <c r="O6" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.8</v>
-      </c>
+        <v>5.6</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="R6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="S6" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
         <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>4</v>
       </c>
       <c r="V6" t="n">
         <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="n">
-        <v>18.3</v>
-      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>VARGUS_D:6</t>
+          <t>DUEM_DCON:7</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1217,12 +1326,12 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>AL41F</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>AlTiN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr"/>
@@ -1233,10 +1342,10 @@
       </c>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="n">
@@ -1244,7 +1353,26 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2021/Groovex VARGUS</t>
+          <t>Ultramini.pdf</t>
+        </is>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>72.98999999999999</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AR6" t="n">
+        <v>6710.24</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
